--- a/raw/K8.xlsx
+++ b/raw/K8.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S_Esbolaeva\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S_Esbolaeva\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\BAZM1KY0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470428C0-354F-480C-8B6D-2FF8C105B34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC8A017-E771-4116-89F9-B6FCC8714BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="7" xr2:uid="{2AA2BCE7-3E7A-403F-B8A7-F4E2406053FD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="9" xr2:uid="{2AA2BCE7-3E7A-403F-B8A7-F4E2406053FD}"/>
   </bookViews>
   <sheets>
     <sheet name="7" sheetId="54" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1964" uniqueCount="118">
   <si>
     <t xml:space="preserve"> ЦДН № 2</t>
   </si>
@@ -397,6 +397,9 @@
   </si>
   <si>
     <t>С 13-Н2851н</t>
+  </si>
+  <si>
+    <t>13-Н2836д</t>
   </si>
 </sst>
 </file>
@@ -606,7 +609,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -632,19 +635,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -720,7 +711,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -821,9 +812,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -848,7 +836,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -867,28 +855,25 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1277,16 +1262,16 @@
       <c r="A2" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="50" t="s">
         <v>91</v>
       </c>
       <c r="C2" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="50" t="s">
         <v>93</v>
       </c>
       <c r="F2" s="30" t="s">
@@ -1304,18 +1289,18 @@
       <c r="J2" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="K2" s="44" t="s">
+      <c r="K2" s="43" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="50" t="s">
         <v>87</v>
       </c>
       <c r="D3" s="30"/>
@@ -1347,7 +1332,7 @@
       <c r="G4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I4" s="10"/>
@@ -1376,7 +1361,7 @@
       <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="44"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="8" t="s">
         <v>58</v>
       </c>
@@ -1441,30 +1426,30 @@
       <c r="A9" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="49" t="s">
         <v>75</v>
       </c>
       <c r="C9" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="38" t="s">
+      <c r="F9" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38" t="s">
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
         <v>67</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="35" t="s">
+      <c r="K9" s="34" t="s">
         <v>27</v>
       </c>
       <c r="L9" s="7"/>
@@ -1477,14 +1462,14 @@
       <c r="B10" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="37" t="s">
+      <c r="D10" s="43"/>
+      <c r="E10" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="37" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="33" t="s">
@@ -1494,7 +1479,7 @@
       <c r="J10" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="35" t="s">
+      <c r="K10" s="34" t="s">
         <v>22</v>
       </c>
       <c r="L10" s="7"/>
@@ -1503,14 +1488,14 @@
       <c r="A11" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="50" t="s">
         <v>98</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="36" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="18" t="s">
@@ -1526,30 +1511,30 @@
       <c r="J11" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="36" t="s">
         <v>44</v>
       </c>
       <c r="L11" s="7"/>
     </row>
     <row r="12" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="49" t="s">
         <v>97</v>
       </c>
       <c r="C12" s="8"/>
-      <c r="E12" s="37" t="s">
+      <c r="E12" s="36" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="38"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="21"/>
       <c r="J12" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="K12" s="37" t="s">
+      <c r="K12" s="36" t="s">
         <v>61</v>
       </c>
       <c r="L12" s="7"/>
@@ -1558,7 +1543,7 @@
       <c r="A13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="49" t="s">
         <v>84</v>
       </c>
       <c r="C13" s="21"/>
@@ -1576,7 +1561,7 @@
       <c r="J13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="36" t="s">
         <v>35</v>
       </c>
       <c r="L13" s="7"/>
@@ -1589,7 +1574,7 @@
         <v>99</v>
       </c>
       <c r="C14" s="21"/>
-      <c r="D14" s="35"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="18" t="s">
         <v>26</v>
       </c>
@@ -1608,11 +1593,11 @@
       <c r="J14" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="K14" s="37"/>
+      <c r="K14" s="36"/>
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="51" t="s">
         <v>95</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -1635,7 +1620,7 @@
       <c r="K15" s="19"/>
     </row>
     <row r="16" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="47"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="18" t="s">
@@ -1651,7 +1636,7 @@
       <c r="I16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="46"/>
+      <c r="J16" s="45"/>
       <c r="K16" s="30"/>
     </row>
     <row r="17" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -1677,7 +1662,7 @@
     </row>
     <row r="18" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="47" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -1687,16 +1672,16 @@
       <c r="F18" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="41" t="s">
         <v>51</v>
       </c>
       <c r="H18" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="44" t="s">
+      <c r="I18" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="46"/>
+      <c r="J18" s="45"/>
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -1719,7 +1704,7 @@
         <v>42</v>
       </c>
       <c r="I19" s="19"/>
-      <c r="J19" s="46"/>
+      <c r="J19" s="45"/>
       <c r="K19" s="5"/>
     </row>
     <row r="20" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1806,7 +1791,7 @@
         <v>47</v>
       </c>
       <c r="I22" s="19"/>
-      <c r="J22" s="46"/>
+      <c r="J22" s="45"/>
       <c r="K22" s="31"/>
     </row>
     <row r="23" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1835,8 +1820,8 @@
         <v>36</v>
       </c>
       <c r="I23" s="19"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="36"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="35"/>
     </row>
     <row r="24" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
@@ -1860,12 +1845,12 @@
       <c r="G24" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="43" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="19"/>
       <c r="J24" s="17"/>
-      <c r="K24" s="39"/>
+      <c r="K24" s="38"/>
     </row>
     <row r="25" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
@@ -1889,10 +1874,10 @@
       <c r="G25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="44"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="39"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="38"/>
     </row>
     <row r="26" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
@@ -1916,9 +1901,9 @@
       <c r="G26" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="42"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="35"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="34"/>
       <c r="K26" s="8"/>
     </row>
     <row r="27" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -1943,9 +1928,9 @@
       <c r="G27" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="42"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="35"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="34"/>
       <c r="K27" s="17"/>
     </row>
     <row r="28" spans="1:25" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -1962,9 +1947,9 @@
       <c r="G28" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="40"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="37"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="36"/>
       <c r="K28" s="21"/>
       <c r="L28" s="32"/>
       <c r="M28" s="32"/>
@@ -1994,7 +1979,7 @@
         <v>26</v>
       </c>
       <c r="I29" s="17"/>
-      <c r="J29" s="37"/>
+      <c r="J29" s="36"/>
       <c r="K29" s="21"/>
     </row>
     <row r="30" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -2014,7 +1999,7 @@
         <v>26</v>
       </c>
       <c r="I30" s="17"/>
-      <c r="J30" s="37"/>
+      <c r="J30" s="36"/>
       <c r="K30" s="21"/>
     </row>
     <row r="31" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -2033,9 +2018,9 @@
       <c r="G31" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="41"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="37"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
       <c r="K31" s="17"/>
     </row>
     <row r="32" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -2054,9 +2039,9 @@
       <c r="G32" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H32" s="41"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="49"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="48"/>
       <c r="K32" s="19"/>
     </row>
     <row r="33" spans="1:11" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2075,32 +2060,32 @@
       <c r="G33" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H33" s="41"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="45"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="44"/>
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2114,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A52B8409-16E1-4C86-8853-D520951A182B}">
-  <dimension ref="A1:Y36"/>
+  <dimension ref="A1:T35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -2130,85 +2115,163 @@
     <col min="11" max="11" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="12"/>
-    </row>
-    <row r="2" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="44"/>
-    </row>
-    <row r="3" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="51"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="51"/>
+    <row r="1" spans="1:11" s="32" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="K2" s="43" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="30"/>
       <c r="E3" s="31"/>
       <c r="F3" s="31"/>
       <c r="G3" s="8"/>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="33"/>
-    </row>
-    <row r="4" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="31"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="J3" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="19"/>
       <c r="D4" s="8"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="43"/>
+      <c r="F4" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>52</v>
+      </c>
       <c r="I4" s="10"/>
       <c r="J4" s="5"/>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A5" s="30"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
+      <c r="C5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>109</v>
+      </c>
       <c r="E5" s="5"/>
       <c r="F5" s="10"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+      <c r="G5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="I5" s="33"/>
       <c r="J5" s="30"/>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="44"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
+    <row r="6" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="43"/>
+      <c r="B6" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="E6" s="9"/>
       <c r="F6" s="10"/>
       <c r="G6" s="8"/>
       <c r="H6" s="9"/>
       <c r="I6" s="10"/>
-      <c r="J6" s="9"/>
+      <c r="J6" s="54"/>
       <c r="K6" s="9"/>
     </row>
-    <row r="7" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="10"/>
@@ -2218,279 +2281,556 @@
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:13" s="32" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="12"/>
+    <row r="8" spans="1:11" s="32" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
+      <c r="H8" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="I8" s="13"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-    </row>
-    <row r="9" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="33"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
+      <c r="J8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
+        <v>67</v>
+      </c>
       <c r="I9" s="16"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-    </row>
-    <row r="10" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="33"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="33"/>
+      <c r="J9" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="K9" s="36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>26</v>
+      </c>
       <c r="I10" s="30"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="7"/>
-    </row>
-    <row r="11" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="8"/>
+      <c r="J10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
+      <c r="E11" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="I11" s="21"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="7"/>
-    </row>
-    <row r="12" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="34"/>
-      <c r="B12" s="30"/>
+      <c r="J11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K11" s="36" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>97</v>
+      </c>
       <c r="C12" s="8"/>
-      <c r="E12" s="37"/>
+      <c r="E12" s="43" t="s">
+        <v>28</v>
+      </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="38"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="21"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="37"/>
-      <c r="L12" s="7"/>
-    </row>
-    <row r="13" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="51"/>
+      <c r="J12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K12" s="36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>84</v>
+      </c>
       <c r="C13" s="21"/>
-      <c r="D13" s="18"/>
+      <c r="D13" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="E13" s="18"/>
       <c r="F13" s="33"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="7"/>
-    </row>
-    <row r="14" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="56"/>
+      <c r="H13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="K13" s="36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>113</v>
+      </c>
       <c r="C14" s="21"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="37"/>
-      <c r="L14" s="7"/>
-    </row>
-    <row r="15" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="53"/>
-      <c r="B15" s="50"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="36"/>
+    </row>
+    <row r="15" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="37"/>
-    </row>
-    <row r="16" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="47"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="36"/>
+    </row>
+    <row r="16" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="46"/>
       <c r="B16" s="8"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="18"/>
+      <c r="E16" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="F16" s="30"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="37"/>
-    </row>
-    <row r="17" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="G16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="45"/>
+      <c r="K16" s="30"/>
+    </row>
+    <row r="17" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="B17" s="8"/>
-      <c r="C17" s="20"/>
+      <c r="C17" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="E17" s="8"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="46"/>
+      <c r="F17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="17"/>
       <c r="K17" s="4"/>
     </row>
-    <row r="18" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="20"/>
+      <c r="C18" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="E18" s="33"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="46"/>
+      <c r="F18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="45"/>
       <c r="K18" s="4"/>
     </row>
-    <row r="19" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="18"/>
+    <row r="19" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="B19" s="30"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
+      <c r="C19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="E19" s="33"/>
-      <c r="F19" s="20"/>
+      <c r="F19" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
+      <c r="H19" s="19" t="s">
+        <v>42</v>
+      </c>
       <c r="I19" s="19"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="5"/>
-    </row>
-    <row r="20" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="36"/>
+    </row>
+    <row r="20" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="B20" s="33"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
+      <c r="C20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="E20" s="33"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="12"/>
+      <c r="F20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>33</v>
+      </c>
       <c r="J20" s="17"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
+    <row r="21" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>34</v>
+      </c>
       <c r="J21" s="21"/>
       <c r="K21" s="5"/>
     </row>
-    <row r="22" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="19"/>
+    <row r="22" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>36</v>
+      </c>
       <c r="I22" s="19"/>
-      <c r="J22" s="46"/>
+      <c r="J22" s="45"/>
       <c r="K22" s="31"/>
     </row>
-    <row r="23" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="19"/>
+    <row r="23" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>46</v>
+      </c>
       <c r="I23" s="19"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="36"/>
-    </row>
-    <row r="24" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="19"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="35"/>
+    </row>
+    <row r="24" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="43"/>
       <c r="I24" s="19"/>
       <c r="J24" s="17"/>
-      <c r="K24" s="39"/>
-    </row>
-    <row r="25" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="39"/>
-    </row>
-    <row r="26" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="35"/>
+      <c r="K24" s="38"/>
+    </row>
+    <row r="25" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="43"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="38"/>
+    </row>
+    <row r="26" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="34"/>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="35"/>
+    <row r="27" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="34"/>
       <c r="K27" s="17"/>
     </row>
-    <row r="28" spans="1:25" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="20"/>
+    <row r="28" spans="1:20" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="B28" s="22"/>
       <c r="C28" s="23"/>
       <c r="D28" s="19"/>
       <c r="E28" s="21"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="37"/>
+      <c r="F28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="36"/>
       <c r="K28" s="21"/>
       <c r="L28" s="32"/>
       <c r="M28" s="32"/>
@@ -2501,101 +2841,122 @@
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="32"/>
-      <c r="U28" s="32"/>
-      <c r="V28" s="32"/>
-      <c r="W28" s="32"/>
-      <c r="X28" s="32"/>
-      <c r="Y28" s="32"/>
-    </row>
-    <row r="29" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A29" s="25"/>
       <c r="B29" s="26"/>
       <c r="C29" s="23"/>
       <c r="D29" s="19"/>
       <c r="E29" s="21"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
+      <c r="F29" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="I29" s="17"/>
-      <c r="J29" s="37"/>
+      <c r="J29" s="36"/>
       <c r="K29" s="21"/>
     </row>
-    <row r="30" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="27"/>
-      <c r="B30" s="13"/>
+    <row r="30" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="13">
+        <v>6</v>
+      </c>
       <c r="C30" s="23"/>
       <c r="D30" s="19"/>
       <c r="E30" s="21"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
+      <c r="F30" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="I30" s="17"/>
-      <c r="J30" s="37"/>
+      <c r="J30" s="36"/>
       <c r="K30" s="21"/>
     </row>
-    <row r="31" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="28"/>
-      <c r="B31" s="13"/>
+    <row r="31" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="13">
+        <v>5</v>
+      </c>
       <c r="C31" s="23"/>
       <c r="D31" s="19"/>
       <c r="E31" s="21"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="37"/>
+      <c r="F31" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
       <c r="K31" s="17"/>
     </row>
-    <row r="32" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="28"/>
-      <c r="B32" s="13"/>
+    <row r="32" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="13">
+        <v>59</v>
+      </c>
       <c r="C32" s="23"/>
       <c r="D32" s="19"/>
       <c r="E32" s="21"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="49"/>
+      <c r="F32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="48"/>
       <c r="K32" s="19"/>
     </row>
     <row r="33" spans="1:11" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="29"/>
-      <c r="B33" s="13"/>
+      <c r="A33" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="13">
+        <v>70</v>
+      </c>
       <c r="C33" s="23"/>
       <c r="D33" s="19"/>
       <c r="E33" s="21"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="45"/>
+      <c r="F33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="44"/>
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A35:K35"/>
-    <mergeCell ref="C36:I36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2659,16 +3020,16 @@
       <c r="A2" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="50" t="s">
         <v>91</v>
       </c>
       <c r="C2" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="50" t="s">
         <v>93</v>
       </c>
       <c r="F2" s="30" t="s">
@@ -2686,18 +3047,18 @@
       <c r="J2" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="K2" s="44" t="s">
+      <c r="K2" s="43" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="50" t="s">
         <v>87</v>
       </c>
       <c r="D3" s="30"/>
@@ -2729,7 +3090,7 @@
       <c r="G4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I4" s="10"/>
@@ -2758,7 +3119,7 @@
       <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="44"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="8" t="s">
         <v>58</v>
       </c>
@@ -2823,30 +3184,30 @@
       <c r="A9" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="49" t="s">
         <v>75</v>
       </c>
       <c r="C9" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="38" t="s">
+      <c r="F9" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38" t="s">
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
         <v>67</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="35" t="s">
+      <c r="K9" s="34" t="s">
         <v>27</v>
       </c>
       <c r="L9" s="7"/>
@@ -2859,14 +3220,14 @@
       <c r="B10" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44" t="s">
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="37" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="33" t="s">
@@ -2876,7 +3237,7 @@
       <c r="J10" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="35" t="s">
+      <c r="K10" s="34" t="s">
         <v>22</v>
       </c>
       <c r="L10" s="7"/>
@@ -2885,14 +3246,14 @@
       <c r="A11" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="50" t="s">
         <v>98</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="43" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="18" t="s">
@@ -2908,30 +3269,30 @@
       <c r="J11" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="36" t="s">
         <v>44</v>
       </c>
       <c r="L11" s="7"/>
     </row>
     <row r="12" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="49" t="s">
         <v>97</v>
       </c>
       <c r="C12" s="8"/>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="43" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="38"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="21"/>
       <c r="J12" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="K12" s="37" t="s">
+      <c r="K12" s="36" t="s">
         <v>61</v>
       </c>
       <c r="L12" s="7"/>
@@ -2940,7 +3301,7 @@
       <c r="A13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="49" t="s">
         <v>84</v>
       </c>
       <c r="C13" s="21"/>
@@ -2958,7 +3319,7 @@
       <c r="J13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="36" t="s">
         <v>35</v>
       </c>
       <c r="L13" s="7"/>
@@ -2971,7 +3332,7 @@
         <v>99</v>
       </c>
       <c r="C14" s="21"/>
-      <c r="D14" s="35"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="18" t="s">
         <v>26</v>
       </c>
@@ -2990,11 +3351,11 @@
       <c r="J14" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="K14" s="37"/>
+      <c r="K14" s="36"/>
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="51" t="s">
         <v>95</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -3017,7 +3378,7 @@
       <c r="K15" s="19"/>
     </row>
     <row r="16" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="47"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="18" t="s">
@@ -3033,7 +3394,7 @@
       <c r="I16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="46"/>
+      <c r="J16" s="45"/>
       <c r="K16" s="30"/>
     </row>
     <row r="17" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -3059,7 +3420,7 @@
     </row>
     <row r="18" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="47" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -3069,16 +3430,16 @@
       <c r="F18" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="41" t="s">
         <v>51</v>
       </c>
       <c r="H18" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="44" t="s">
+      <c r="I18" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="46"/>
+      <c r="J18" s="45"/>
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -3101,7 +3462,7 @@
         <v>42</v>
       </c>
       <c r="I19" s="19"/>
-      <c r="J19" s="46"/>
+      <c r="J19" s="45"/>
       <c r="K19" s="5"/>
     </row>
     <row r="20" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3188,7 +3549,7 @@
         <v>47</v>
       </c>
       <c r="I22" s="19"/>
-      <c r="J22" s="46"/>
+      <c r="J22" s="45"/>
       <c r="K22" s="31"/>
     </row>
     <row r="23" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3217,8 +3578,8 @@
         <v>36</v>
       </c>
       <c r="I23" s="19"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="36"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="35"/>
     </row>
     <row r="24" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
@@ -3242,12 +3603,12 @@
       <c r="G24" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="43" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="19"/>
       <c r="J24" s="17"/>
-      <c r="K24" s="39"/>
+      <c r="K24" s="38"/>
     </row>
     <row r="25" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
@@ -3271,10 +3632,10 @@
       <c r="G25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="44"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="39"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="38"/>
     </row>
     <row r="26" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
@@ -3298,9 +3659,9 @@
       <c r="G26" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="42"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="35"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="34"/>
       <c r="K26" s="8"/>
     </row>
     <row r="27" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -3325,9 +3686,9 @@
       <c r="G27" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="42"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="35"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="34"/>
       <c r="K27" s="17"/>
     </row>
     <row r="28" spans="1:25" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -3344,9 +3705,9 @@
       <c r="G28" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="40"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="37"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="36"/>
       <c r="K28" s="21"/>
       <c r="L28" s="32"/>
       <c r="M28" s="32"/>
@@ -3376,7 +3737,7 @@
         <v>26</v>
       </c>
       <c r="I29" s="17"/>
-      <c r="J29" s="37"/>
+      <c r="J29" s="36"/>
       <c r="K29" s="21"/>
     </row>
     <row r="30" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -3396,7 +3757,7 @@
         <v>26</v>
       </c>
       <c r="I30" s="17"/>
-      <c r="J30" s="37"/>
+      <c r="J30" s="36"/>
       <c r="K30" s="21"/>
     </row>
     <row r="31" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -3415,9 +3776,9 @@
       <c r="G31" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="41"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="37"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
       <c r="K31" s="17"/>
     </row>
     <row r="32" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -3436,9 +3797,9 @@
       <c r="G32" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H32" s="41"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="49"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="48"/>
       <c r="K32" s="19"/>
     </row>
     <row r="33" spans="1:11" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3457,32 +3818,32 @@
       <c r="G33" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H33" s="41"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="45"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="44"/>
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3550,16 +3911,16 @@
       <c r="A2" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="50" t="s">
         <v>91</v>
       </c>
       <c r="C2" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="50" t="s">
         <v>93</v>
       </c>
       <c r="F2" s="30" t="s">
@@ -3577,18 +3938,18 @@
       <c r="J2" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="K2" s="44" t="s">
+      <c r="K2" s="43" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="50" t="s">
         <v>87</v>
       </c>
       <c r="D3" s="30"/>
@@ -3622,7 +3983,7 @@
       <c r="G4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I4" s="10"/>
@@ -3651,7 +4012,7 @@
       <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="44"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="8" t="s">
         <v>58</v>
       </c>
@@ -3716,30 +4077,30 @@
       <c r="A9" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="49" t="s">
         <v>75</v>
       </c>
       <c r="C9" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="38" t="s">
+      <c r="F9" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38" t="s">
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
         <v>67</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="35" t="s">
+      <c r="K9" s="34" t="s">
         <v>27</v>
       </c>
       <c r="L9" s="7"/>
@@ -3752,14 +4113,14 @@
       <c r="B10" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44" t="s">
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="37" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="33" t="s">
@@ -3769,7 +4130,7 @@
       <c r="J10" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="35" t="s">
+      <c r="K10" s="34" t="s">
         <v>22</v>
       </c>
       <c r="L10" s="7"/>
@@ -3778,14 +4139,14 @@
       <c r="A11" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="50" t="s">
         <v>98</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="43" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="18" t="s">
@@ -3801,30 +4162,30 @@
       <c r="J11" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="36" t="s">
         <v>44</v>
       </c>
       <c r="L11" s="7"/>
     </row>
     <row r="12" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="49" t="s">
         <v>97</v>
       </c>
       <c r="C12" s="8"/>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="43" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="38"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="21"/>
       <c r="J12" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="K12" s="37" t="s">
+      <c r="K12" s="36" t="s">
         <v>61</v>
       </c>
       <c r="L12" s="7"/>
@@ -3833,7 +4194,7 @@
       <c r="A13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="49" t="s">
         <v>84</v>
       </c>
       <c r="C13" s="21"/>
@@ -3851,7 +4212,7 @@
       <c r="J13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="36" t="s">
         <v>35</v>
       </c>
       <c r="L13" s="7"/>
@@ -3864,7 +4225,7 @@
         <v>99</v>
       </c>
       <c r="C14" s="21"/>
-      <c r="D14" s="35"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="18" t="s">
         <v>26</v>
       </c>
@@ -3883,11 +4244,11 @@
       <c r="J14" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="K14" s="37"/>
+      <c r="K14" s="36"/>
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="51" t="s">
         <v>95</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -3910,7 +4271,7 @@
       <c r="K15" s="19"/>
     </row>
     <row r="16" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="47"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="18" t="s">
@@ -3926,7 +4287,7 @@
       <c r="I16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="46"/>
+      <c r="J16" s="45"/>
       <c r="K16" s="30"/>
     </row>
     <row r="17" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -3952,7 +4313,7 @@
     </row>
     <row r="18" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="47" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -3962,16 +4323,16 @@
       <c r="F18" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="41" t="s">
         <v>51</v>
       </c>
       <c r="H18" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="44" t="s">
+      <c r="I18" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="46"/>
+      <c r="J18" s="45"/>
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -3994,7 +4355,7 @@
         <v>42</v>
       </c>
       <c r="I19" s="19"/>
-      <c r="J19" s="46"/>
+      <c r="J19" s="45"/>
       <c r="K19" s="5"/>
     </row>
     <row r="20" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4081,7 +4442,7 @@
         <v>36</v>
       </c>
       <c r="I22" s="19"/>
-      <c r="J22" s="46"/>
+      <c r="J22" s="45"/>
       <c r="K22" s="31"/>
     </row>
     <row r="23" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4106,12 +4467,12 @@
       <c r="G23" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="43" t="s">
         <v>30</v>
       </c>
       <c r="I23" s="19"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="36"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="35"/>
     </row>
     <row r="24" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
@@ -4135,10 +4496,10 @@
       <c r="G24" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="44"/>
+      <c r="H24" s="43"/>
       <c r="I24" s="19"/>
       <c r="J24" s="17"/>
-      <c r="K24" s="39"/>
+      <c r="K24" s="38"/>
     </row>
     <row r="25" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
@@ -4162,10 +4523,10 @@
       <c r="G25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="44"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="39"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="38"/>
     </row>
     <row r="26" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
@@ -4189,9 +4550,9 @@
       <c r="G26" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="42"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="35"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="34"/>
       <c r="K26" s="8"/>
     </row>
     <row r="27" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -4216,9 +4577,9 @@
       <c r="G27" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="42"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="35"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="34"/>
       <c r="K27" s="17"/>
     </row>
     <row r="28" spans="1:25" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -4235,9 +4596,9 @@
       <c r="G28" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="40"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="37"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="36"/>
       <c r="K28" s="21"/>
       <c r="L28" s="32"/>
       <c r="M28" s="32"/>
@@ -4267,7 +4628,7 @@
         <v>26</v>
       </c>
       <c r="I29" s="17"/>
-      <c r="J29" s="37"/>
+      <c r="J29" s="36"/>
       <c r="K29" s="21"/>
     </row>
     <row r="30" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -4287,7 +4648,7 @@
         <v>26</v>
       </c>
       <c r="I30" s="17"/>
-      <c r="J30" s="37"/>
+      <c r="J30" s="36"/>
       <c r="K30" s="21"/>
     </row>
     <row r="31" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -4306,9 +4667,9 @@
       <c r="G31" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="41"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="37"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
       <c r="K31" s="17"/>
     </row>
     <row r="32" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -4327,9 +4688,9 @@
       <c r="G32" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H32" s="41"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="49"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="48"/>
       <c r="K32" s="19"/>
     </row>
     <row r="33" spans="1:11" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4348,32 +4709,32 @@
       <c r="G33" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H33" s="41"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="45"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="44"/>
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4442,16 +4803,16 @@
       <c r="A2" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="50" t="s">
         <v>91</v>
       </c>
       <c r="C2" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="50" t="s">
         <v>93</v>
       </c>
       <c r="F2" s="30" t="s">
@@ -4469,18 +4830,18 @@
       <c r="J2" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="K2" s="44" t="s">
+      <c r="K2" s="43" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="53" t="s">
         <v>87</v>
       </c>
       <c r="D3" s="30"/>
@@ -4489,7 +4850,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
-      <c r="J3" s="55" t="s">
+      <c r="J3" s="53" t="s">
         <v>100</v>
       </c>
       <c r="K3" s="33" t="s">
@@ -4514,7 +4875,7 @@
       <c r="G4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I4" s="10"/>
@@ -4543,7 +4904,7 @@
       <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="44"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="8" t="s">
         <v>58</v>
       </c>
@@ -4608,30 +4969,30 @@
       <c r="A9" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="49" t="s">
         <v>75</v>
       </c>
       <c r="C9" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="38" t="s">
+      <c r="F9" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38" t="s">
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
         <v>67</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="35" t="s">
+      <c r="K9" s="34" t="s">
         <v>27</v>
       </c>
       <c r="L9" s="7"/>
@@ -4644,14 +5005,14 @@
       <c r="B10" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44" t="s">
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="37" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="33" t="s">
@@ -4661,7 +5022,7 @@
       <c r="J10" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="35" t="s">
+      <c r="K10" s="34" t="s">
         <v>22</v>
       </c>
       <c r="L10" s="7"/>
@@ -4670,14 +5031,14 @@
       <c r="A11" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="50" t="s">
         <v>98</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="43" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="18" t="s">
@@ -4693,30 +5054,30 @@
       <c r="J11" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="36" t="s">
         <v>44</v>
       </c>
       <c r="L11" s="7"/>
     </row>
     <row r="12" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="49" t="s">
         <v>97</v>
       </c>
       <c r="C12" s="8"/>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="43" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="38"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="21"/>
       <c r="J12" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="K12" s="37" t="s">
+      <c r="K12" s="36" t="s">
         <v>61</v>
       </c>
       <c r="L12" s="7"/>
@@ -4725,7 +5086,7 @@
       <c r="A13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="49" t="s">
         <v>84</v>
       </c>
       <c r="C13" s="21"/>
@@ -4743,7 +5104,7 @@
       <c r="J13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="36" t="s">
         <v>35</v>
       </c>
       <c r="L13" s="7"/>
@@ -4756,7 +5117,7 @@
         <v>99</v>
       </c>
       <c r="C14" s="21"/>
-      <c r="D14" s="35"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="18" t="s">
         <v>26</v>
       </c>
@@ -4775,11 +5136,11 @@
       <c r="J14" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="K14" s="37"/>
+      <c r="K14" s="36"/>
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="51" t="s">
         <v>95</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -4804,7 +5165,7 @@
       <c r="K15" s="19"/>
     </row>
     <row r="16" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="47"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="18" t="s">
@@ -4820,7 +5181,7 @@
       <c r="I16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="46"/>
+      <c r="J16" s="45"/>
       <c r="K16" s="30"/>
     </row>
     <row r="17" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -4846,7 +5207,7 @@
     </row>
     <row r="18" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="47" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -4856,16 +5217,16 @@
       <c r="F18" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="41" t="s">
         <v>51</v>
       </c>
       <c r="H18" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="44" t="s">
+      <c r="I18" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="46"/>
+      <c r="J18" s="45"/>
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -4888,7 +5249,7 @@
         <v>42</v>
       </c>
       <c r="I19" s="19"/>
-      <c r="J19" s="46"/>
+      <c r="J19" s="45"/>
       <c r="K19" s="5"/>
     </row>
     <row r="20" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4975,7 +5336,7 @@
         <v>36</v>
       </c>
       <c r="I22" s="19"/>
-      <c r="J22" s="46"/>
+      <c r="J22" s="45"/>
       <c r="K22" s="31"/>
     </row>
     <row r="23" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -5000,10 +5361,10 @@
       <c r="G23" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H23" s="44"/>
+      <c r="H23" s="43"/>
       <c r="I23" s="19"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="36"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="35"/>
     </row>
     <row r="24" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
@@ -5027,10 +5388,10 @@
       <c r="G24" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="44"/>
+      <c r="H24" s="43"/>
       <c r="I24" s="19"/>
       <c r="J24" s="17"/>
-      <c r="K24" s="39"/>
+      <c r="K24" s="38"/>
     </row>
     <row r="25" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
@@ -5054,10 +5415,10 @@
       <c r="G25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="44"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="39"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="38"/>
     </row>
     <row r="26" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
@@ -5081,9 +5442,9 @@
       <c r="G26" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="42"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="35"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="34"/>
       <c r="K26" s="8"/>
     </row>
     <row r="27" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -5108,9 +5469,9 @@
       <c r="G27" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="42"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="35"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="34"/>
       <c r="K27" s="17"/>
     </row>
     <row r="28" spans="1:25" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -5127,9 +5488,9 @@
       <c r="G28" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="40"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="37"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="36"/>
       <c r="K28" s="21"/>
       <c r="L28" s="32"/>
       <c r="M28" s="32"/>
@@ -5159,7 +5520,7 @@
         <v>26</v>
       </c>
       <c r="I29" s="17"/>
-      <c r="J29" s="37"/>
+      <c r="J29" s="36"/>
       <c r="K29" s="21"/>
     </row>
     <row r="30" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -5179,7 +5540,7 @@
         <v>26</v>
       </c>
       <c r="I30" s="17"/>
-      <c r="J30" s="37"/>
+      <c r="J30" s="36"/>
       <c r="K30" s="21"/>
     </row>
     <row r="31" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -5198,9 +5559,9 @@
       <c r="G31" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="41"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="37"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
       <c r="K31" s="17"/>
     </row>
     <row r="32" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -5219,9 +5580,9 @@
       <c r="G32" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H32" s="41"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="49"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="48"/>
       <c r="K32" s="19"/>
     </row>
     <row r="33" spans="1:11" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -5240,32 +5601,32 @@
       <c r="G33" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H33" s="41"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="45"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="44"/>
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5334,16 +5695,16 @@
       <c r="A2" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="50" t="s">
         <v>91</v>
       </c>
       <c r="C2" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="50" t="s">
         <v>93</v>
       </c>
       <c r="F2" s="30" t="s">
@@ -5361,18 +5722,18 @@
       <c r="J2" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="K2" s="44" t="s">
+      <c r="K2" s="43" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="53" t="s">
         <v>87</v>
       </c>
       <c r="D3" s="30"/>
@@ -5381,7 +5742,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
-      <c r="J3" s="55" t="s">
+      <c r="J3" s="53" t="s">
         <v>100</v>
       </c>
       <c r="K3" s="33" t="s">
@@ -5406,7 +5767,7 @@
       <c r="G4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I4" s="10"/>
@@ -5435,7 +5796,7 @@
       <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="44"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="8" t="s">
         <v>58</v>
       </c>
@@ -5500,30 +5861,30 @@
       <c r="A9" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="49" t="s">
         <v>75</v>
       </c>
       <c r="C9" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="38" t="s">
+      <c r="F9" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38" t="s">
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
         <v>67</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="35" t="s">
+      <c r="K9" s="34" t="s">
         <v>27</v>
       </c>
       <c r="L9" s="7"/>
@@ -5536,14 +5897,14 @@
       <c r="B10" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44" t="s">
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="37" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="33" t="s">
@@ -5553,7 +5914,7 @@
       <c r="J10" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="35" t="s">
+      <c r="K10" s="34" t="s">
         <v>22</v>
       </c>
       <c r="L10" s="7"/>
@@ -5562,14 +5923,14 @@
       <c r="A11" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="50" t="s">
         <v>98</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="43" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="18" t="s">
@@ -5585,30 +5946,30 @@
       <c r="J11" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="36" t="s">
         <v>44</v>
       </c>
       <c r="L11" s="7"/>
     </row>
     <row r="12" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="49" t="s">
         <v>97</v>
       </c>
       <c r="C12" s="8"/>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="43" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="38"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="21"/>
       <c r="J12" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="K12" s="37" t="s">
+      <c r="K12" s="36" t="s">
         <v>61</v>
       </c>
       <c r="L12" s="7"/>
@@ -5617,7 +5978,7 @@
       <c r="A13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="49" t="s">
         <v>84</v>
       </c>
       <c r="C13" s="21"/>
@@ -5635,7 +5996,7 @@
       <c r="J13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="36" t="s">
         <v>35</v>
       </c>
       <c r="L13" s="7"/>
@@ -5648,7 +6009,7 @@
         <v>99</v>
       </c>
       <c r="C14" s="21"/>
-      <c r="D14" s="35"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="18" t="s">
         <v>26</v>
       </c>
@@ -5667,11 +6028,11 @@
       <c r="J14" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="K14" s="37"/>
+      <c r="K14" s="36"/>
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="51" t="s">
         <v>95</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -5696,7 +6057,7 @@
       <c r="K15" s="19"/>
     </row>
     <row r="16" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="47"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="18" t="s">
@@ -5712,7 +6073,7 @@
       <c r="I16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="46"/>
+      <c r="J16" s="45"/>
       <c r="K16" s="30"/>
     </row>
     <row r="17" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -5738,7 +6099,7 @@
     </row>
     <row r="18" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="47" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -5748,16 +6109,16 @@
       <c r="F18" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="41" t="s">
         <v>51</v>
       </c>
       <c r="H18" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="44" t="s">
+      <c r="I18" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="46"/>
+      <c r="J18" s="45"/>
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -5780,7 +6141,7 @@
         <v>42</v>
       </c>
       <c r="I19" s="19"/>
-      <c r="J19" s="46"/>
+      <c r="J19" s="45"/>
       <c r="K19" s="5"/>
     </row>
     <row r="20" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -5867,7 +6228,7 @@
         <v>36</v>
       </c>
       <c r="I22" s="19"/>
-      <c r="J22" s="46"/>
+      <c r="J22" s="45"/>
       <c r="K22" s="31"/>
     </row>
     <row r="23" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -5892,10 +6253,10 @@
       <c r="G23" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H23" s="44"/>
+      <c r="H23" s="43"/>
       <c r="I23" s="19"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="36"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="35"/>
     </row>
     <row r="24" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
@@ -5919,10 +6280,10 @@
       <c r="G24" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="44"/>
+      <c r="H24" s="43"/>
       <c r="I24" s="19"/>
       <c r="J24" s="17"/>
-      <c r="K24" s="39"/>
+      <c r="K24" s="38"/>
     </row>
     <row r="25" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
@@ -5946,10 +6307,10 @@
       <c r="G25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="44"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="39"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="38"/>
     </row>
     <row r="26" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
@@ -5973,9 +6334,9 @@
       <c r="G26" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="42"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="35"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="34"/>
       <c r="K26" s="8"/>
     </row>
     <row r="27" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -6000,9 +6361,9 @@
       <c r="G27" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="42"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="35"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="34"/>
       <c r="K27" s="17"/>
     </row>
     <row r="28" spans="1:25" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -6019,9 +6380,9 @@
       <c r="G28" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="40"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="37"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="36"/>
       <c r="K28" s="21"/>
       <c r="L28" s="32"/>
       <c r="M28" s="32"/>
@@ -6051,7 +6412,7 @@
         <v>26</v>
       </c>
       <c r="I29" s="17"/>
-      <c r="J29" s="37"/>
+      <c r="J29" s="36"/>
       <c r="K29" s="21"/>
     </row>
     <row r="30" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -6071,7 +6432,7 @@
         <v>26</v>
       </c>
       <c r="I30" s="17"/>
-      <c r="J30" s="37"/>
+      <c r="J30" s="36"/>
       <c r="K30" s="21"/>
     </row>
     <row r="31" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -6090,9 +6451,9 @@
       <c r="G31" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="41"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="37"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
       <c r="K31" s="17"/>
     </row>
     <row r="32" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -6111,9 +6472,9 @@
       <c r="G32" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H32" s="41"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="49"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="48"/>
       <c r="K32" s="19"/>
     </row>
     <row r="33" spans="1:11" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6132,32 +6493,32 @@
       <c r="G33" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H33" s="41"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="45"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="44"/>
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6226,16 +6587,16 @@
       <c r="A2" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="53" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="50" t="s">
         <v>93</v>
       </c>
       <c r="F2" s="30" t="s">
@@ -6253,15 +6614,15 @@
       <c r="J2" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="K2" s="44" t="s">
+      <c r="K2" s="43" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="49" t="s">
         <v>105</v>
       </c>
       <c r="C3" s="31" t="s">
@@ -6273,7 +6634,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
-      <c r="J3" s="55" t="s">
+      <c r="J3" s="53" t="s">
         <v>94</v>
       </c>
       <c r="K3" s="33" t="s">
@@ -6296,7 +6657,7 @@
       <c r="G4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I4" s="10"/>
@@ -6325,7 +6686,7 @@
       <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:14" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="44"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="8" t="s">
         <v>58</v>
       </c>
@@ -6383,7 +6744,7 @@
       <c r="K8" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="37"/>
+      <c r="L8" s="36"/>
       <c r="M8" s="7"/>
     </row>
     <row r="9" spans="1:14" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -6396,28 +6757,28 @@
       <c r="C9" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="38" t="s">
+      <c r="F9" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38" t="s">
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
         <v>67</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:14" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A10" s="33" t="s">
@@ -6426,14 +6787,14 @@
       <c r="B10" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44" t="s">
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="37" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="33" t="s">
@@ -6443,7 +6804,7 @@
       <c r="J10" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="37" t="s">
+      <c r="K10" s="36" t="s">
         <v>22</v>
       </c>
       <c r="L10" s="7"/>
@@ -6452,14 +6813,14 @@
       <c r="A11" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="50" t="s">
         <v>112</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="43" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="18" t="s">
@@ -6475,41 +6836,41 @@
       <c r="J11" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="L11" s="37"/>
-      <c r="N11" s="37"/>
+      <c r="L11" s="36"/>
+      <c r="N11" s="36"/>
     </row>
     <row r="12" spans="1:14" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="49" t="s">
         <v>97</v>
       </c>
       <c r="C12" s="8"/>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="43" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="38"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="21"/>
       <c r="J12" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="K12" s="37" t="s">
+      <c r="K12" s="36" t="s">
         <v>61</v>
       </c>
       <c r="L12" s="7"/>
-      <c r="N12" s="37"/>
+      <c r="N12" s="36"/>
     </row>
     <row r="13" spans="1:14" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="49" t="s">
         <v>84</v>
       </c>
       <c r="C13" s="21"/>
@@ -6527,11 +6888,11 @@
       <c r="J13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="36" t="s">
         <v>35</v>
       </c>
       <c r="L13" s="7"/>
-      <c r="N13" s="37"/>
+      <c r="N13" s="36"/>
     </row>
     <row r="14" spans="1:14" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
@@ -6541,7 +6902,7 @@
         <v>113</v>
       </c>
       <c r="C14" s="21"/>
-      <c r="D14" s="35"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="18" t="s">
         <v>26</v>
       </c>
@@ -6560,14 +6921,14 @@
       <c r="J14" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="K14" s="37" t="s">
+      <c r="K14" s="36" t="s">
         <v>78</v>
       </c>
       <c r="L14" s="7"/>
-      <c r="N14" s="37"/>
+      <c r="N14" s="36"/>
     </row>
     <row r="15" spans="1:14" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="51" t="s">
         <v>108</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -6587,10 +6948,10 @@
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
       <c r="J15" s="17"/>
-      <c r="K15" s="37"/>
+      <c r="K15" s="36"/>
     </row>
     <row r="16" spans="1:14" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="47"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="18" t="s">
@@ -6606,7 +6967,7 @@
       <c r="I16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="46"/>
+      <c r="J16" s="45"/>
       <c r="K16" s="30"/>
     </row>
     <row r="17" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -6629,11 +6990,11 @@
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="4"/>
-      <c r="P17" s="37"/>
+      <c r="P17" s="36"/>
     </row>
     <row r="18" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="47" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -6643,16 +7004,16 @@
       <c r="F18" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="41" t="s">
         <v>51</v>
       </c>
       <c r="H18" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="44" t="s">
+      <c r="I18" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="46"/>
+      <c r="J18" s="45"/>
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -6675,8 +7036,8 @@
         <v>42</v>
       </c>
       <c r="I19" s="19"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="37"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="36"/>
     </row>
     <row r="20" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
@@ -6762,7 +7123,7 @@
         <v>36</v>
       </c>
       <c r="I22" s="19"/>
-      <c r="J22" s="46"/>
+      <c r="J22" s="45"/>
       <c r="K22" s="31"/>
     </row>
     <row r="23" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6791,8 +7152,8 @@
         <v>46</v>
       </c>
       <c r="I23" s="19"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="36"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="35"/>
     </row>
     <row r="24" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
@@ -6816,10 +7177,10 @@
       <c r="G24" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="44"/>
+      <c r="H24" s="43"/>
       <c r="I24" s="19"/>
       <c r="J24" s="17"/>
-      <c r="K24" s="39"/>
+      <c r="K24" s="38"/>
     </row>
     <row r="25" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
@@ -6843,11 +7204,11 @@
       <c r="G25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="44"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="39"/>
-      <c r="M25" s="37"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="38"/>
+      <c r="M25" s="36"/>
     </row>
     <row r="26" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
@@ -6871,11 +7232,11 @@
       <c r="G26" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="42"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="35"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="34"/>
       <c r="K26" s="8"/>
-      <c r="M26" s="37"/>
+      <c r="M26" s="36"/>
     </row>
     <row r="27" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A27" s="20" t="s">
@@ -6899,9 +7260,9 @@
       <c r="G27" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="42"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="35"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="34"/>
       <c r="K27" s="17"/>
     </row>
     <row r="28" spans="1:25" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -6918,9 +7279,9 @@
       <c r="G28" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="40"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="37"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="36"/>
       <c r="K28" s="21"/>
       <c r="L28" s="32"/>
       <c r="M28" s="32"/>
@@ -6950,7 +7311,7 @@
         <v>26</v>
       </c>
       <c r="I29" s="17"/>
-      <c r="J29" s="37"/>
+      <c r="J29" s="36"/>
       <c r="K29" s="21"/>
     </row>
     <row r="30" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -6970,7 +7331,7 @@
         <v>26</v>
       </c>
       <c r="I30" s="17"/>
-      <c r="J30" s="37"/>
+      <c r="J30" s="36"/>
       <c r="K30" s="21"/>
     </row>
     <row r="31" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -6989,9 +7350,9 @@
       <c r="G31" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="41"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="37"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
       <c r="K31" s="17"/>
     </row>
     <row r="32" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -7010,9 +7371,9 @@
       <c r="G32" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H32" s="41"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="49"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="48"/>
       <c r="K32" s="19"/>
     </row>
     <row r="33" spans="1:11" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7031,35 +7392,35 @@
       <c r="G33" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H33" s="41"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="45"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="44"/>
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="37"/>
-      <c r="H36" s="37"/>
-      <c r="I36" s="37"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G38" s="37"/>
+      <c r="G38" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7126,16 +7487,16 @@
       <c r="A2" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="50" t="s">
         <v>93</v>
       </c>
       <c r="F2" s="30" t="s">
@@ -7153,15 +7514,15 @@
       <c r="J2" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="K2" s="44" t="s">
+      <c r="K2" s="43" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="49" t="s">
         <v>105</v>
       </c>
       <c r="C3" s="31" t="s">
@@ -7196,7 +7557,7 @@
       <c r="G4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I4" s="10"/>
@@ -7225,7 +7586,7 @@
       <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="44"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="8" t="s">
         <v>58</v>
       </c>
@@ -7240,7 +7601,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="9"/>
       <c r="I6" s="10"/>
-      <c r="J6" s="57"/>
+      <c r="J6" s="54"/>
       <c r="K6" s="9"/>
     </row>
     <row r="7" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -7294,24 +7655,24 @@
       <c r="C9" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="54" t="s">
+      <c r="F9" s="52" t="s">
         <v>116</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38" t="s">
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
         <v>67</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="36" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7322,14 +7683,14 @@
       <c r="B10" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44" t="s">
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="37" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="33" t="s">
@@ -7339,7 +7700,7 @@
       <c r="J10" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="37" t="s">
+      <c r="K10" s="36" t="s">
         <v>22</v>
       </c>
     </row>
@@ -7347,14 +7708,14 @@
       <c r="A11" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="50" t="s">
         <v>112</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="43" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="18" t="s">
@@ -7370,29 +7731,29 @@
       <c r="J11" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="36" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="49" t="s">
         <v>97</v>
       </c>
       <c r="C12" s="8"/>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="43" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="38"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="21"/>
       <c r="J12" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="K12" s="37" t="s">
+      <c r="K12" s="36" t="s">
         <v>61</v>
       </c>
     </row>
@@ -7400,7 +7761,7 @@
       <c r="A13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="49" t="s">
         <v>84</v>
       </c>
       <c r="C13" s="21"/>
@@ -7418,7 +7779,7 @@
       <c r="J13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="36" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7430,7 +7791,7 @@
         <v>113</v>
       </c>
       <c r="C14" s="21"/>
-      <c r="D14" s="35"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="18" t="s">
         <v>26</v>
       </c>
@@ -7447,12 +7808,12 @@
         <v>26</v>
       </c>
       <c r="J14" s="17"/>
-      <c r="K14" s="37" t="s">
+      <c r="K14" s="36" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="51" t="s">
         <v>108</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -7472,10 +7833,10 @@
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
       <c r="J15" s="17"/>
-      <c r="K15" s="37"/>
+      <c r="K15" s="36"/>
     </row>
     <row r="16" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="47"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="18" t="s">
@@ -7491,7 +7852,7 @@
       <c r="I16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="46"/>
+      <c r="J16" s="45"/>
       <c r="K16" s="30"/>
     </row>
     <row r="17" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -7517,7 +7878,7 @@
     </row>
     <row r="18" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="47" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -7527,16 +7888,16 @@
       <c r="F18" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="41" t="s">
         <v>51</v>
       </c>
       <c r="H18" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="44" t="s">
+      <c r="I18" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="46"/>
+      <c r="J18" s="45"/>
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -7559,8 +7920,8 @@
         <v>42</v>
       </c>
       <c r="I19" s="19"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="37"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="36"/>
     </row>
     <row r="20" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
@@ -7646,7 +8007,7 @@
         <v>36</v>
       </c>
       <c r="I22" s="19"/>
-      <c r="J22" s="46"/>
+      <c r="J22" s="45"/>
       <c r="K22" s="31"/>
     </row>
     <row r="23" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7675,8 +8036,8 @@
         <v>46</v>
       </c>
       <c r="I23" s="19"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="36"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="35"/>
     </row>
     <row r="24" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
@@ -7700,10 +8061,10 @@
       <c r="G24" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="44"/>
+      <c r="H24" s="43"/>
       <c r="I24" s="19"/>
       <c r="J24" s="17"/>
-      <c r="K24" s="39"/>
+      <c r="K24" s="38"/>
     </row>
     <row r="25" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
@@ -7727,10 +8088,10 @@
       <c r="G25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="44"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="39"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="38"/>
     </row>
     <row r="26" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
@@ -7754,9 +8115,9 @@
       <c r="G26" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="42"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="35"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="34"/>
       <c r="K26" s="8"/>
     </row>
     <row r="27" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -7781,9 +8142,9 @@
       <c r="G27" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="42"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="35"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="34"/>
       <c r="K27" s="17"/>
     </row>
     <row r="28" spans="1:20" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -7800,9 +8161,9 @@
       <c r="G28" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="40"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="37"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="36"/>
       <c r="K28" s="21"/>
       <c r="L28" s="32"/>
       <c r="M28" s="32"/>
@@ -7827,7 +8188,7 @@
         <v>26</v>
       </c>
       <c r="I29" s="17"/>
-      <c r="J29" s="37"/>
+      <c r="J29" s="36"/>
       <c r="K29" s="21"/>
     </row>
     <row r="30" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -7847,7 +8208,7 @@
         <v>26</v>
       </c>
       <c r="I30" s="17"/>
-      <c r="J30" s="37"/>
+      <c r="J30" s="36"/>
       <c r="K30" s="21"/>
     </row>
     <row r="31" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -7866,9 +8227,9 @@
       <c r="G31" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="41"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="37"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
       <c r="K31" s="17"/>
     </row>
     <row r="32" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -7887,9 +8248,9 @@
       <c r="G32" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H32" s="41"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="49"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="48"/>
       <c r="K32" s="19"/>
     </row>
     <row r="33" spans="1:11" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7908,23 +8269,23 @@
       <c r="G33" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H33" s="41"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="45"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="44"/>
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7992,16 +8353,16 @@
       <c r="A2" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="50" t="s">
         <v>93</v>
       </c>
       <c r="F2" s="30" t="s">
@@ -8019,15 +8380,15 @@
       <c r="J2" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="K2" s="44" t="s">
+      <c r="K2" s="43" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="49" t="s">
         <v>105</v>
       </c>
       <c r="C3" s="31" t="s">
@@ -8062,7 +8423,7 @@
       <c r="G4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="42" t="s">
         <v>52</v>
       </c>
       <c r="I4" s="10"/>
@@ -8091,7 +8452,7 @@
       <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="44"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="8" t="s">
         <v>58</v>
       </c>
@@ -8106,7 +8467,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="9"/>
       <c r="I6" s="10"/>
-      <c r="J6" s="57"/>
+      <c r="J6" s="54"/>
       <c r="K6" s="9"/>
     </row>
     <row r="7" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -8160,24 +8521,24 @@
       <c r="C9" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="54" t="s">
+      <c r="F9" s="52" t="s">
         <v>116</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38" t="s">
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
         <v>67</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="36" t="s">
         <v>27</v>
       </c>
     </row>
@@ -8188,14 +8549,14 @@
       <c r="B10" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44" t="s">
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="37" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="33" t="s">
@@ -8205,7 +8566,7 @@
       <c r="J10" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="37" t="s">
+      <c r="K10" s="36" t="s">
         <v>22</v>
       </c>
     </row>
@@ -8213,14 +8574,14 @@
       <c r="A11" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="50" t="s">
         <v>112</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="43" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="18" t="s">
@@ -8236,29 +8597,29 @@
       <c r="J11" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="36" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="49" t="s">
         <v>97</v>
       </c>
       <c r="C12" s="8"/>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="43" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="38"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="21"/>
       <c r="J12" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="K12" s="37" t="s">
+      <c r="K12" s="36" t="s">
         <v>61</v>
       </c>
     </row>
@@ -8266,7 +8627,7 @@
       <c r="A13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="49" t="s">
         <v>84</v>
       </c>
       <c r="C13" s="21"/>
@@ -8284,7 +8645,7 @@
       <c r="J13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="36" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8296,7 +8657,7 @@
         <v>113</v>
       </c>
       <c r="C14" s="21"/>
-      <c r="D14" s="35"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="18" t="s">
         <v>26</v>
       </c>
@@ -8313,10 +8674,10 @@
         <v>26</v>
       </c>
       <c r="J14" s="17"/>
-      <c r="K14" s="37"/>
+      <c r="K14" s="36"/>
     </row>
     <row r="15" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="51" t="s">
         <v>108</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -8336,10 +8697,10 @@
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
       <c r="J15" s="17"/>
-      <c r="K15" s="37"/>
+      <c r="K15" s="36"/>
     </row>
     <row r="16" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="47"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="18" t="s">
@@ -8355,7 +8716,7 @@
       <c r="I16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="46"/>
+      <c r="J16" s="45"/>
       <c r="K16" s="30"/>
     </row>
     <row r="17" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -8381,7 +8742,7 @@
     </row>
     <row r="18" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="47" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -8391,16 +8752,16 @@
       <c r="F18" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="41" t="s">
         <v>51</v>
       </c>
       <c r="H18" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="44" t="s">
+      <c r="I18" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="46"/>
+      <c r="J18" s="45"/>
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -8423,8 +8784,8 @@
         <v>42</v>
       </c>
       <c r="I19" s="19"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="37"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="36"/>
     </row>
     <row r="20" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
@@ -8510,7 +8871,7 @@
         <v>36</v>
       </c>
       <c r="I22" s="19"/>
-      <c r="J22" s="46"/>
+      <c r="J22" s="45"/>
       <c r="K22" s="31"/>
     </row>
     <row r="23" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8539,8 +8900,8 @@
         <v>46</v>
       </c>
       <c r="I23" s="19"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="36"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="35"/>
     </row>
     <row r="24" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
@@ -8564,10 +8925,10 @@
       <c r="G24" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="44"/>
+      <c r="H24" s="43"/>
       <c r="I24" s="19"/>
       <c r="J24" s="17"/>
-      <c r="K24" s="39"/>
+      <c r="K24" s="38"/>
     </row>
     <row r="25" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
@@ -8591,10 +8952,10 @@
       <c r="G25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="44"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="39"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="38"/>
     </row>
     <row r="26" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
@@ -8618,9 +8979,9 @@
       <c r="G26" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="42"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="35"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="34"/>
       <c r="K26" s="8"/>
     </row>
     <row r="27" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -8645,9 +9006,9 @@
       <c r="G27" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="42"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="35"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="34"/>
       <c r="K27" s="17"/>
     </row>
     <row r="28" spans="1:20" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -8664,9 +9025,9 @@
       <c r="G28" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="40"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="37"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="36"/>
       <c r="K28" s="21"/>
       <c r="L28" s="32"/>
       <c r="M28" s="32"/>
@@ -8691,7 +9052,7 @@
         <v>26</v>
       </c>
       <c r="I29" s="17"/>
-      <c r="J29" s="37"/>
+      <c r="J29" s="36"/>
       <c r="K29" s="21"/>
     </row>
     <row r="30" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -8711,7 +9072,7 @@
         <v>26</v>
       </c>
       <c r="I30" s="17"/>
-      <c r="J30" s="37"/>
+      <c r="J30" s="36"/>
       <c r="K30" s="21"/>
     </row>
     <row r="31" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -8730,9 +9091,9 @@
       <c r="G31" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="41"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="37"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
       <c r="K31" s="17"/>
     </row>
     <row r="32" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -8751,9 +9112,9 @@
       <c r="G32" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H32" s="41"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="49"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="48"/>
       <c r="K32" s="19"/>
     </row>
     <row r="33" spans="1:11" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8772,23 +9133,23 @@
       <c r="G33" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H33" s="41"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="45"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="44"/>
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8801,7 +9162,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57ED581D-968E-468B-A358-A9730CFF40E5}">
-  <dimension ref="A1:Y36"/>
+  <dimension ref="A1:T35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -8817,85 +9178,163 @@
     <col min="11" max="11" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="12"/>
-    </row>
-    <row r="2" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="44"/>
-    </row>
-    <row r="3" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="51"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="51"/>
+    <row r="1" spans="1:11" s="32" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="K2" s="43" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="30"/>
       <c r="E3" s="31"/>
       <c r="F3" s="31"/>
       <c r="G3" s="8"/>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="33"/>
-    </row>
-    <row r="4" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="31"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="J3" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="19"/>
       <c r="D4" s="8"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="43"/>
+      <c r="F4" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>52</v>
+      </c>
       <c r="I4" s="10"/>
       <c r="J4" s="5"/>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A5" s="30"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
+      <c r="C5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>109</v>
+      </c>
       <c r="E5" s="5"/>
       <c r="F5" s="10"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+      <c r="G5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="I5" s="33"/>
       <c r="J5" s="30"/>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="44"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
+    <row r="6" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="43"/>
+      <c r="B6" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="E6" s="9"/>
       <c r="F6" s="10"/>
       <c r="G6" s="8"/>
       <c r="H6" s="9"/>
       <c r="I6" s="10"/>
-      <c r="J6" s="9"/>
+      <c r="J6" s="54"/>
       <c r="K6" s="9"/>
     </row>
-    <row r="7" spans="1:13" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="10"/>
@@ -8905,279 +9344,554 @@
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:13" s="32" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="12"/>
+    <row r="8" spans="1:11" s="32" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
+      <c r="H8" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="I8" s="13"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-    </row>
-    <row r="9" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="33"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
+      <c r="J8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
+        <v>67</v>
+      </c>
       <c r="I9" s="16"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-    </row>
-    <row r="10" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="33"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="33"/>
+      <c r="J9" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="K9" s="36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>26</v>
+      </c>
       <c r="I10" s="30"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="7"/>
-    </row>
-    <row r="11" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="8"/>
+      <c r="J10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
+      <c r="E11" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="I11" s="21"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="7"/>
-    </row>
-    <row r="12" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="34"/>
-      <c r="B12" s="30"/>
+      <c r="J11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K11" s="36" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>97</v>
+      </c>
       <c r="C12" s="8"/>
-      <c r="E12" s="37"/>
+      <c r="E12" s="43" t="s">
+        <v>28</v>
+      </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="38"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="21"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="37"/>
-      <c r="L12" s="7"/>
-    </row>
-    <row r="13" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="51"/>
+      <c r="J12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K12" s="36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>84</v>
+      </c>
       <c r="C13" s="21"/>
-      <c r="D13" s="18"/>
+      <c r="D13" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="E13" s="18"/>
       <c r="F13" s="33"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="7"/>
-    </row>
-    <row r="14" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="56"/>
+      <c r="H13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" s="36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>113</v>
+      </c>
       <c r="C14" s="21"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="37"/>
-      <c r="L14" s="7"/>
-    </row>
-    <row r="15" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="53"/>
-      <c r="B15" s="50"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="17"/>
+      <c r="K14" s="36"/>
+    </row>
+    <row r="15" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="37"/>
-    </row>
-    <row r="16" spans="1:13" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="47"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="36"/>
+    </row>
+    <row r="16" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="46"/>
       <c r="B16" s="8"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="18"/>
+      <c r="E16" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="F16" s="30"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="37"/>
-    </row>
-    <row r="17" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="G16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="45"/>
+      <c r="K16" s="30"/>
+    </row>
+    <row r="17" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="B17" s="8"/>
-      <c r="C17" s="20"/>
+      <c r="C17" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="E17" s="8"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="46"/>
+      <c r="F17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="17"/>
       <c r="K17" s="4"/>
     </row>
-    <row r="18" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="20"/>
+      <c r="C18" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="E18" s="33"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="46"/>
+      <c r="F18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="45"/>
       <c r="K18" s="4"/>
     </row>
-    <row r="19" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="18"/>
+    <row r="19" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="B19" s="30"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
+      <c r="C19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="E19" s="33"/>
-      <c r="F19" s="20"/>
+      <c r="F19" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
+      <c r="H19" s="19" t="s">
+        <v>42</v>
+      </c>
       <c r="I19" s="19"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="5"/>
-    </row>
-    <row r="20" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="36"/>
+    </row>
+    <row r="20" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="B20" s="33"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
+      <c r="C20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="E20" s="33"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="12"/>
+      <c r="F20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>33</v>
+      </c>
       <c r="J20" s="17"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
+    <row r="21" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>34</v>
+      </c>
       <c r="J21" s="21"/>
       <c r="K21" s="5"/>
     </row>
-    <row r="22" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="19"/>
+    <row r="22" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>36</v>
+      </c>
       <c r="I22" s="19"/>
-      <c r="J22" s="46"/>
+      <c r="J22" s="45"/>
       <c r="K22" s="31"/>
     </row>
-    <row r="23" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="19"/>
+    <row r="23" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>46</v>
+      </c>
       <c r="I23" s="19"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="36"/>
-    </row>
-    <row r="24" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="19"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="35"/>
+    </row>
+    <row r="24" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="43"/>
       <c r="I24" s="19"/>
       <c r="J24" s="17"/>
-      <c r="K24" s="39"/>
-    </row>
-    <row r="25" spans="1:25" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="39"/>
-    </row>
-    <row r="26" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="35"/>
+      <c r="K24" s="38"/>
+    </row>
+    <row r="25" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="43"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="38"/>
+    </row>
+    <row r="26" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="34"/>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="35"/>
+    <row r="27" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="34"/>
       <c r="K27" s="17"/>
     </row>
-    <row r="28" spans="1:25" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="20"/>
+    <row r="28" spans="1:20" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="B28" s="22"/>
       <c r="C28" s="23"/>
       <c r="D28" s="19"/>
       <c r="E28" s="21"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="37"/>
+      <c r="F28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="36"/>
       <c r="K28" s="21"/>
       <c r="L28" s="32"/>
       <c r="M28" s="32"/>
@@ -9188,101 +9902,122 @@
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="32"/>
-      <c r="U28" s="32"/>
-      <c r="V28" s="32"/>
-      <c r="W28" s="32"/>
-      <c r="X28" s="32"/>
-      <c r="Y28" s="32"/>
-    </row>
-    <row r="29" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A29" s="25"/>
       <c r="B29" s="26"/>
       <c r="C29" s="23"/>
       <c r="D29" s="19"/>
       <c r="E29" s="21"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
+      <c r="F29" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="I29" s="17"/>
-      <c r="J29" s="37"/>
+      <c r="J29" s="36"/>
       <c r="K29" s="21"/>
     </row>
-    <row r="30" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="27"/>
-      <c r="B30" s="13"/>
+    <row r="30" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="13">
+        <v>5</v>
+      </c>
       <c r="C30" s="23"/>
       <c r="D30" s="19"/>
       <c r="E30" s="21"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
+      <c r="F30" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="I30" s="17"/>
-      <c r="J30" s="37"/>
+      <c r="J30" s="36"/>
       <c r="K30" s="21"/>
     </row>
-    <row r="31" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="28"/>
-      <c r="B31" s="13"/>
+    <row r="31" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="13">
+        <v>5</v>
+      </c>
       <c r="C31" s="23"/>
       <c r="D31" s="19"/>
       <c r="E31" s="21"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="37"/>
+      <c r="F31" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
       <c r="K31" s="17"/>
     </row>
-    <row r="32" spans="1:25" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="28"/>
-      <c r="B32" s="13"/>
+    <row r="32" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="13">
+        <v>60</v>
+      </c>
       <c r="C32" s="23"/>
       <c r="D32" s="19"/>
       <c r="E32" s="21"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="49"/>
+      <c r="F32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="48"/>
       <c r="K32" s="19"/>
     </row>
     <row r="33" spans="1:11" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="29"/>
-      <c r="B33" s="13"/>
+      <c r="A33" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="13">
+        <v>70</v>
+      </c>
       <c r="C33" s="23"/>
       <c r="D33" s="19"/>
       <c r="E33" s="21"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="45"/>
+      <c r="F33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="44"/>
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A35:K35"/>
-    <mergeCell ref="C36:I36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/raw/K8.xlsx
+++ b/raw/K8.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S_Esbolaeva\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\BAZM1KY0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S_Esbolaeva\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E0ACD8-ED11-4EEB-8D62-BB0A3B459F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8497E6-95D2-4FFD-BC3F-31FF7E53BC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="9" xr2:uid="{2AA2BCE7-3E7A-403F-B8A7-F4E2406053FD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="10" xr2:uid="{2AA2BCE7-3E7A-403F-B8A7-F4E2406053FD}"/>
   </bookViews>
   <sheets>
     <sheet name="7" sheetId="54" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="14" sheetId="61" r:id="rId8"/>
     <sheet name="15" sheetId="62" r:id="rId9"/>
     <sheet name="26" sheetId="63" r:id="rId10"/>
+    <sheet name="27" sheetId="64" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="123">
   <si>
     <t xml:space="preserve"> ЦДН № 2</t>
   </si>
@@ -409,6 +410,12 @@
   </si>
   <si>
     <t>20-Н344912</t>
+  </si>
+  <si>
+    <t>13-Н2848н</t>
+  </si>
+  <si>
+    <t>55-д</t>
   </si>
 </sst>
 </file>
@@ -720,7 +727,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -883,6 +890,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2075,26 +2088,26 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="56"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2190,9 +2203,6 @@
       <c r="J2" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="K2" s="33" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="3" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A3" s="55" t="s">
@@ -2213,7 +2223,9 @@
       <c r="J3" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="K3" s="33"/>
+      <c r="K3" s="33" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A4" s="31" t="s">
@@ -2953,17 +2965,889 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="56"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A35:K35"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1112354A-E705-4BBA-AAC7-C64D88FFD5BD}">
+  <dimension ref="A1:T35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="32" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="J2" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="K2" s="57" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="9"/>
+    </row>
+    <row r="5" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="30"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="33"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="9"/>
+    </row>
+    <row r="6" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="43"/>
+      <c r="B6" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="9"/>
+    </row>
+    <row r="7" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+    </row>
+    <row r="8" spans="1:11" s="32" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="13"/>
+      <c r="J8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="16"/>
+      <c r="J9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="30"/>
+      <c r="J10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="21"/>
+      <c r="J11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K11" s="36" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="E12" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K12" s="36" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="18"/>
+      <c r="F13" s="33"/>
+      <c r="H13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="36" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15" s="36" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="46"/>
+      <c r="B16" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="30"/>
+      <c r="G16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="45"/>
+      <c r="K16" s="30"/>
+    </row>
+    <row r="17" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="B17" s="8"/>
+      <c r="C17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="17"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="8"/>
+      <c r="C18" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="33"/>
+      <c r="F18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="45"/>
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="33"/>
+      <c r="F19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="19"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="36"/>
+    </row>
+    <row r="20" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="33"/>
+      <c r="C20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="33"/>
+      <c r="F20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="17"/>
+      <c r="K20" s="4"/>
+    </row>
+    <row r="21" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="J21" s="21"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="I22" s="19"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="31"/>
+    </row>
+    <row r="23" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" s="19"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="35"/>
+    </row>
+    <row r="24" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="43"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="38"/>
+    </row>
+    <row r="25" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="43"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="38"/>
+    </row>
+    <row r="26" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="8"/>
+    </row>
+    <row r="27" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:20" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+    </row>
+    <row r="29" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="25"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="17"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="21"/>
+    </row>
+    <row r="30" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="13">
+        <v>7</v>
+      </c>
+      <c r="C30" s="23"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="17"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="21"/>
+    </row>
+    <row r="31" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="13">
+        <v>7</v>
+      </c>
+      <c r="C31" s="23"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="13">
+        <v>56</v>
+      </c>
+      <c r="C32" s="23"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="19"/>
+    </row>
+    <row r="33" spans="1:11" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="13">
+        <v>70</v>
+      </c>
+      <c r="C33" s="23"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="19"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3835,26 +4719,26 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="56"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4726,26 +5610,26 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="56"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5618,26 +6502,26 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="56"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6510,26 +7394,26 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="56"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7409,17 +8293,17 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="56"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C36" s="36"/>
@@ -8286,17 +9170,17 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="56"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9150,17 +10034,17 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="56"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10014,17 +10898,17 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="56"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/raw/K8.xlsx
+++ b/raw/K8.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S_Esbolaeva\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8497E6-95D2-4FFD-BC3F-31FF7E53BC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F02D444-12CF-40ED-8545-F29AC974B963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="10" xr2:uid="{2AA2BCE7-3E7A-403F-B8A7-F4E2406053FD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="11" xr2:uid="{2AA2BCE7-3E7A-403F-B8A7-F4E2406053FD}"/>
   </bookViews>
   <sheets>
     <sheet name="7" sheetId="54" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="15" sheetId="62" r:id="rId9"/>
     <sheet name="26" sheetId="63" r:id="rId10"/>
     <sheet name="27" sheetId="64" r:id="rId11"/>
+    <sheet name="28" sheetId="65" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="123">
   <si>
     <t xml:space="preserve"> ЦДН № 2</t>
   </si>
@@ -3858,6 +3859,877 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650367D8-4AA9-4B49-9061-E780C3F87BF7}">
+  <dimension ref="A1:T35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="32" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="J2" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="K2" s="57" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="9"/>
+    </row>
+    <row r="5" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="30"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="33"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="9"/>
+    </row>
+    <row r="6" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="43"/>
+      <c r="B6" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="9"/>
+    </row>
+    <row r="7" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+    </row>
+    <row r="8" spans="1:11" s="32" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="13"/>
+      <c r="J8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="16"/>
+      <c r="J9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="30"/>
+      <c r="J10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="21"/>
+      <c r="J11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K11" s="36" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="E12" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K12" s="36" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="18"/>
+      <c r="F13" s="33"/>
+      <c r="H13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" s="36" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="36" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="46"/>
+      <c r="B16" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="30"/>
+      <c r="G16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="45"/>
+      <c r="K16" s="30"/>
+    </row>
+    <row r="17" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="B17" s="8"/>
+      <c r="C17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="17"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="8"/>
+      <c r="C18" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="33"/>
+      <c r="F18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="45"/>
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="33"/>
+      <c r="F19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="19"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="36"/>
+    </row>
+    <row r="20" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="33"/>
+      <c r="C20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="33"/>
+      <c r="F20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="17"/>
+      <c r="K20" s="4"/>
+    </row>
+    <row r="21" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="J21" s="21"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I22" s="19"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="31"/>
+    </row>
+    <row r="23" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" s="19"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="35"/>
+    </row>
+    <row r="24" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="19"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="38"/>
+    </row>
+    <row r="25" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="43"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="38"/>
+    </row>
+    <row r="26" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="8"/>
+    </row>
+    <row r="27" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:20" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+    </row>
+    <row r="29" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="25"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="17"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="21"/>
+    </row>
+    <row r="30" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="13">
+        <v>6</v>
+      </c>
+      <c r="C30" s="23"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="17"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="21"/>
+    </row>
+    <row r="31" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="13">
+        <v>7</v>
+      </c>
+      <c r="C31" s="23"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="13">
+        <v>57</v>
+      </c>
+      <c r="C32" s="23"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="19"/>
+    </row>
+    <row r="33" spans="1:11" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="13">
+        <v>70</v>
+      </c>
+      <c r="C33" s="23"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="19"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A35:K35"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC3BE61-2D5C-4BF7-8574-95E78D4C82CE}">
   <dimension ref="A1:Y36"/>

--- a/raw/K8.xlsx
+++ b/raw/K8.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S_Esbolaeva\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S_Esbolaeva\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\BAZM1KY0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F02D444-12CF-40ED-8545-F29AC974B963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FD0F08-CBB9-4B2C-AF3F-CA8B2F007900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="11" xr2:uid="{2AA2BCE7-3E7A-403F-B8A7-F4E2406053FD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="12" xr2:uid="{2AA2BCE7-3E7A-403F-B8A7-F4E2406053FD}"/>
   </bookViews>
   <sheets>
     <sheet name="7" sheetId="54" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="26" sheetId="63" r:id="rId10"/>
     <sheet name="27" sheetId="64" r:id="rId11"/>
     <sheet name="28" sheetId="65" r:id="rId12"/>
+    <sheet name="29" sheetId="66" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2563" uniqueCount="125">
   <si>
     <t xml:space="preserve"> ЦДН № 2</t>
   </si>
@@ -418,6 +419,12 @@
   <si>
     <t>55-д</t>
   </si>
+  <si>
+    <t>С 13-Н2828</t>
+  </si>
+  <si>
+    <t>С 13-Н2852н</t>
+  </si>
 </sst>
 </file>
 
@@ -728,7 +735,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -897,6 +904,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2089,26 +2099,26 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
+      <c r="C36" s="60"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2966,17 +2976,17 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3838,17 +3848,17 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4710,23 +4720,897 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A35:K35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5824F0C2-2898-498D-B823-3CF1E0710C39}">
+  <dimension ref="A1:T35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="32" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="J2" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="K2" s="57" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="9"/>
+    </row>
+    <row r="5" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="30"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="33"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="9"/>
+    </row>
+    <row r="6" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="43"/>
+      <c r="B6" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="9"/>
+    </row>
+    <row r="7" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+    </row>
+    <row r="8" spans="1:11" s="32" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="13"/>
+      <c r="J8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="16"/>
+      <c r="J9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="30"/>
+      <c r="J10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="21"/>
+      <c r="J11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K11" s="36" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="E12" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K12" s="36" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="18"/>
+      <c r="F13" s="33"/>
+      <c r="H13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="K14" s="36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="46"/>
+      <c r="B16" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="30"/>
+      <c r="G16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="45"/>
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="B17" s="8"/>
+      <c r="C17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="17"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="8"/>
+      <c r="C18" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="33"/>
+      <c r="F18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="45"/>
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="33"/>
+      <c r="F19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="19"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="36"/>
+    </row>
+    <row r="20" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="33"/>
+      <c r="C20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="33"/>
+      <c r="F20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="17"/>
+      <c r="K20" s="4"/>
+    </row>
+    <row r="21" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="J21" s="21"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I22" s="19"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="31"/>
+    </row>
+    <row r="23" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" s="19"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="35"/>
+    </row>
+    <row r="24" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="19"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="38"/>
+    </row>
+    <row r="25" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="43"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="38"/>
+    </row>
+    <row r="26" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="8"/>
+    </row>
+    <row r="27" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:20" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+    </row>
+    <row r="29" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="25"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="17"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="21"/>
+    </row>
+    <row r="30" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="13">
+        <v>6</v>
+      </c>
+      <c r="C30" s="23"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="17"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="21"/>
+    </row>
+    <row r="31" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="13">
+        <v>7</v>
+      </c>
+      <c r="C31" s="23"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="13">
+        <v>57</v>
+      </c>
+      <c r="C32" s="23"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="19"/>
+    </row>
+    <row r="33" spans="1:11" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="13">
+        <v>70</v>
+      </c>
+      <c r="C33" s="23"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="19"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A35:K35"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5591,26 +6475,26 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
+      <c r="C36" s="60"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6482,26 +7366,26 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
+      <c r="C36" s="60"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7374,26 +8258,26 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
+      <c r="C36" s="60"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8266,26 +9150,26 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
+      <c r="C36" s="60"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9165,17 +10049,17 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C36" s="36"/>
@@ -10042,17 +10926,17 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10906,17 +11790,17 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11770,17 +12654,17 @@
       <c r="K33" s="19"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/raw/K8.xlsx
+++ b/raw/K8.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S_Esbolaeva\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\BAZM1KY0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FD0F08-CBB9-4B2C-AF3F-CA8B2F007900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64ACFBD-E2A0-4A5A-B196-C56EF4280508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="12" xr2:uid="{2AA2BCE7-3E7A-403F-B8A7-F4E2406053FD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="13" xr2:uid="{2AA2BCE7-3E7A-403F-B8A7-F4E2406053FD}"/>
   </bookViews>
   <sheets>
     <sheet name="7" sheetId="54" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="27" sheetId="64" r:id="rId11"/>
     <sheet name="28" sheetId="65" r:id="rId12"/>
     <sheet name="29" sheetId="66" r:id="rId13"/>
+    <sheet name="30" sheetId="67" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2563" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2765" uniqueCount="130">
   <si>
     <t xml:space="preserve"> ЦДН № 2</t>
   </si>
@@ -425,6 +426,21 @@
   <si>
     <t>С 13-Н2852н</t>
   </si>
+  <si>
+    <t>13-Н2847</t>
+  </si>
+  <si>
+    <t>13-779BUд</t>
+  </si>
+  <si>
+    <t>13-Н2833н</t>
+  </si>
+  <si>
+    <t>13-Н2833д</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  13-Н2852д</t>
+  </si>
 </sst>
 </file>
 
@@ -633,7 +649,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -672,6 +688,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -735,7 +757,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -915,6 +937,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal_Sheet1" xfId="4" xr:uid="{4C891039-7410-42A5-AED8-315FF353E864}"/>
@@ -927,8 +952,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF33CC"/>
       <color rgb="FF009900"/>
-      <color rgb="FFFF33CC"/>
       <color rgb="FF0000FF"/>
     </mruColors>
   </colors>
@@ -5614,6 +5639,884 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE7529D9-456F-423F-A83A-812A382D1EF8}">
+  <dimension ref="A1:T35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="32" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="J2" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="K2" s="57" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="9"/>
+    </row>
+    <row r="5" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="30"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="33"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="9"/>
+    </row>
+    <row r="6" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="43"/>
+      <c r="B6" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="9"/>
+    </row>
+    <row r="7" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+    </row>
+    <row r="8" spans="1:11" s="32" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="13"/>
+      <c r="J8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="16"/>
+      <c r="J9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="30"/>
+      <c r="J10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="21"/>
+      <c r="J11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K11" s="36" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="E12" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K12" s="36" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="18"/>
+      <c r="F13" s="33"/>
+      <c r="H13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="K14" s="36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="K15" s="36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="46"/>
+      <c r="B16" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="30"/>
+      <c r="G16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="45"/>
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="B17" s="8"/>
+      <c r="C17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="17"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="8"/>
+      <c r="C18" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="33"/>
+      <c r="F18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="45"/>
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="33"/>
+      <c r="F19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="19"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="36"/>
+    </row>
+    <row r="20" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="33"/>
+      <c r="C20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="33"/>
+      <c r="F20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="17"/>
+      <c r="K20" s="4"/>
+    </row>
+    <row r="21" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="J21" s="21"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I22" s="19"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="31"/>
+    </row>
+    <row r="23" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" s="19"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="35"/>
+    </row>
+    <row r="24" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="19"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="38"/>
+    </row>
+    <row r="25" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="43"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="38"/>
+    </row>
+    <row r="26" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="8"/>
+    </row>
+    <row r="27" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:20" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+    </row>
+    <row r="29" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="25"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="17"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="21"/>
+    </row>
+    <row r="30" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="13">
+        <v>7</v>
+      </c>
+      <c r="C30" s="23"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="17"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="21"/>
+    </row>
+    <row r="31" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="13">
+        <v>7</v>
+      </c>
+      <c r="C31" s="23"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="13">
+        <v>56</v>
+      </c>
+      <c r="C32" s="23"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="19"/>
+    </row>
+    <row r="33" spans="1:11" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="13">
+        <v>70</v>
+      </c>
+      <c r="C33" s="23"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="19"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A35:K35"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC3BE61-2D5C-4BF7-8574-95E78D4C82CE}">
   <dimension ref="A1:Y36"/>

--- a/raw/K8.xlsx
+++ b/raw/K8.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S_Esbolaeva\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\BAZM1KY0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64ACFBD-E2A0-4A5A-B196-C56EF4280508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D3EB2D-31C2-44DC-94F0-6D4A1524DB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="13" xr2:uid="{2AA2BCE7-3E7A-403F-B8A7-F4E2406053FD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="14" xr2:uid="{2AA2BCE7-3E7A-403F-B8A7-F4E2406053FD}"/>
   </bookViews>
   <sheets>
     <sheet name="7" sheetId="54" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="28" sheetId="65" r:id="rId12"/>
     <sheet name="29" sheetId="66" r:id="rId13"/>
     <sheet name="30" sheetId="67" r:id="rId14"/>
+    <sheet name="31" sheetId="68" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2765" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2967" uniqueCount="132">
   <si>
     <t xml:space="preserve"> ЦДН № 2</t>
   </si>
@@ -441,6 +442,12 @@
   <si>
     <t xml:space="preserve">  13-Н2852д</t>
   </si>
+  <si>
+    <t xml:space="preserve">  13-Н2890н</t>
+  </si>
+  <si>
+    <t>13-Н2879н</t>
+  </si>
 </sst>
 </file>
 
@@ -649,7 +656,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -688,12 +695,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -757,7 +758,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -936,9 +937,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5696,8 +5694,8 @@
       <c r="A2" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="61" t="s">
-        <v>104</v>
+      <c r="B2" s="53" t="s">
+        <v>130</v>
       </c>
       <c r="C2" s="53" t="s">
         <v>106</v>
@@ -5731,8 +5729,8 @@
       <c r="A3" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="55" t="s">
-        <v>105</v>
+      <c r="B3" s="49" t="s">
+        <v>131</v>
       </c>
       <c r="C3" s="31" t="s">
         <v>78</v>
@@ -6459,6 +6457,883 @@
       </c>
       <c r="B32" s="13">
         <v>56</v>
+      </c>
+      <c r="C32" s="23"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="19"/>
+    </row>
+    <row r="33" spans="1:11" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="13">
+        <v>70</v>
+      </c>
+      <c r="C33" s="23"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="19"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A35:K35"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75090F7-075B-4E24-BEEF-E25DC6F2E74F}">
+  <dimension ref="A1:T35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="32" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="J2" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="K2" s="57" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="9"/>
+    </row>
+    <row r="5" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="30"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="33"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="9"/>
+    </row>
+    <row r="6" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="43"/>
+      <c r="B6" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="9"/>
+    </row>
+    <row r="7" spans="1:11" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+    </row>
+    <row r="8" spans="1:11" s="32" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="13"/>
+      <c r="J8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="16"/>
+      <c r="J9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="30"/>
+      <c r="J10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="21"/>
+      <c r="J11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K11" s="36" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K12" s="36" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="18"/>
+      <c r="F13" s="33"/>
+      <c r="H13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="K14" s="36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="K15" s="36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="46"/>
+      <c r="B16" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="30"/>
+      <c r="G16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="B17" s="8"/>
+      <c r="C17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="17"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="8"/>
+      <c r="C18" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="33"/>
+      <c r="F18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="45"/>
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="33"/>
+      <c r="F19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="19"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="36"/>
+    </row>
+    <row r="20" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="33"/>
+      <c r="C20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="33"/>
+      <c r="F20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="17"/>
+      <c r="K20" s="4"/>
+    </row>
+    <row r="21" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="J21" s="21"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I22" s="19"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="31"/>
+    </row>
+    <row r="23" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" s="19"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="35"/>
+    </row>
+    <row r="24" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="19"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="38"/>
+    </row>
+    <row r="25" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="43"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="38"/>
+    </row>
+    <row r="26" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="8"/>
+    </row>
+    <row r="27" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:20" s="24" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="39"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+    </row>
+    <row r="29" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="25"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="17"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="21"/>
+    </row>
+    <row r="30" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="13">
+        <v>8</v>
+      </c>
+      <c r="C30" s="23"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="17"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="21"/>
+    </row>
+    <row r="31" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="13">
+        <v>7</v>
+      </c>
+      <c r="C31" s="23"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="1:20" s="32" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="13">
+        <v>55</v>
       </c>
       <c r="C32" s="23"/>
       <c r="D32" s="19"/>
